--- a/Confluence/data_contract_attribute_spec_v5.xlsx
+++ b/Confluence/data_contract_attribute_spec_v5.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,6 +140,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -762,7 +767,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>producer_app</t>
+          <t>source.app</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -802,7 +807,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>producer_domain</t>
+          <t>source.domain</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -842,7 +847,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>business_owner</t>
+          <t>owner.business</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -882,7 +887,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>technical_owner</t>
+          <t>owner.technical</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -922,7 +927,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>steward_email</t>
+          <t>owner.email</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -962,7 +967,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>contract_version</t>
+          <t>contract.version</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -1122,7 +1127,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>grain</t>
+          <t>contract.grain</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -1202,7 +1207,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>table_shape</t>
+          <t>shape</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -1402,7 +1407,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>refresh_frequency</t>
+          <t>refresh.freq</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>refresh_sla</t>
+          <t>refresh.sla</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>contract_last_changed</t>
+          <t>contract.changed</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -1682,7 +1687,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>data_classification</t>
+          <t>class.sensitivity</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -1722,7 +1727,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>pii_present</t>
+          <t>class.pii</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -2762,7 +2767,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>contract_yaml_path</t>
+          <t>contract.yaml_path</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -2802,7 +2807,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>contract_ref</t>
+          <t>contract.ref</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -2842,7 +2847,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>collibra_ref</t>
+          <t>collibra.ref</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -2952,7 +2957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -3065,78 +3070,134 @@
       <c r="A18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>What changed in v6 vs v5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>• Renamed UC tag 'grain' → 'contract.grain' for consistency with the namespace rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>• Product-layer tags sheet removed from the standards workbook — this spec is now the single source for product attributes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>• Aligned all UC tag keys with the dotted-namespace rule. 15 keys renamed (e.g. business_owner → owner.business, refresh_frequency → refresh.freq, data_classification → class.sensitivity). Now consistent with the standards workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>What changed in v5 vs v3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>• Added reference_dependencies block — declares upstream reference data (FX, taxonomy, calendar) with source AND conformed status</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>• Added composability block — explicit safely_joinable_with, reconciliation_required_with, reconciliation_resolved_for (for derived products)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>• Added currency_handling block — native vs pre-converted, FX source used, FX rate date</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>• Added known_issues block — declared gaps with severity, tracking reference, target resolution</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>• Restructured all sheets so Category is its own filterable column (was merged section header)</t>
+          <t>• Added reference_dependencies block — declares upstream reference data (FX, taxonomy, calendar) with source AND conformed status</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr"/>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>• Added composability block — explicit safely_joinable_with, reconciliation_required_with, reconciliation_resolved_for (for derived products)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Companion artifact</t>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>• Added currency_handling block — native vs pre-converted, FX source used, FX rate date</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
+          <t>• Added known_issues block — declared gaps with severity, tracking reference, target resolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>• Restructured all sheets so Category is its own filterable column (was merged section header)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Companion artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
           <t>This spec is for product owners authoring data contracts. For app owners onboarding application schemas, see the separate uc_metadata_standards workbook (App-layer tags sheet). Some app-layer tags are inherited automatically by products via CI — see the contract spec REFERENCE DEPENDENCIES and inheritance notes.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Deferred — tag conventions for core, core_model, analytics</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Tag conventions for these layers will be defined when those layers are implemented. Expected to be a small extension of the app-layer tag set with conformance markers added (conformed=true, table_shape, etc.) but NO contract tags — these layers carry risk-internal infrastructure, not contracted external products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Naming rule — namespace with four bare exceptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>UC tag keys use dotted-namespace form. Four exceptions are bare (no namespace) because they are the most heavily filtered universal classifiers: capability · archetype · shape · status. Everything else follows the namespace rule including contract.grain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Single source of truth for product authoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>This spec is the single source of truth for product attributes — used by product owners authoring derived/consumer-aligned contracts, and by app owners authoring foundational contracts. The UC-tag column shows which attributes also surface as Unity Catalog tags. The standards workbook (uc_metadata_standards_v4.xlsx) covers app-layer tags and column-level standards separately.</t>
         </is>
       </c>
     </row>
